--- a/agent/schedule/project-data/11_项目交付场景信息/项目交付场景信息表.xlsx
+++ b/agent/schedule/project-data/11_项目交付场景信息/项目交付场景信息表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>产品代际</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -123,6 +123,12 @@
   <si>
     <t>集群集成</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目名称</t>
+  </si>
+  <si>
+    <t>A3液冷集群集成</t>
   </si>
 </sst>
 </file>
@@ -533,8 +539,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -542,9 +548,10 @@
     <col min="3" max="4" width="12.26953125" customWidth="1"/>
     <col min="5" max="5" width="12.54296875" customWidth="1"/>
     <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -572,8 +579,11 @@
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -600,6 +610,9 @@
       </c>
       <c r="I2" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
